--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N99_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N99_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.45818483530137</v>
+        <v>11.93695503573647</v>
       </c>
       <c r="D2" t="n">
-        <v>67.10646559287365</v>
+        <v>10.90480065884197</v>
       </c>
       <c r="E2" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F2" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.1523371902279</v>
+        <v>12.69975479341203</v>
       </c>
       <c r="D3" t="n">
-        <v>65.51912862353788</v>
+        <v>10.64685840132491</v>
       </c>
       <c r="E3" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F3" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.48518607441403</v>
+        <v>10.47884273709228</v>
       </c>
       <c r="D4" t="n">
-        <v>63.32456079595025</v>
+        <v>10.29024112934192</v>
       </c>
       <c r="E4" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F4" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.34521212488298</v>
+        <v>4.281096970293484</v>
       </c>
       <c r="D5" t="n">
-        <v>25.90813063803011</v>
+        <v>4.210071228679893</v>
       </c>
       <c r="E5" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F5" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.83672300389125</v>
+        <v>2.735967488132328</v>
       </c>
       <c r="D6" t="n">
-        <v>16.42954124644066</v>
+        <v>2.669800452546607</v>
       </c>
       <c r="E6" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F6" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.62515673072359</v>
+        <v>3.839087968742584</v>
       </c>
       <c r="D7" t="n">
-        <v>6.519202405202649</v>
+        <v>1.059370390845431</v>
       </c>
       <c r="E7" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F7" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35958452813988</v>
+        <v>2.98343248582273</v>
       </c>
       <c r="D8" t="n">
-        <v>17.90426114941805</v>
+        <v>2.909442436780434</v>
       </c>
       <c r="E8" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F8" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39633589021694</v>
+        <v>4.939404582160253</v>
       </c>
       <c r="D9" t="n">
-        <v>30.69464249862627</v>
+        <v>4.987879406026768</v>
       </c>
       <c r="E9" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F9" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>67.05401368842351</v>
+        <v>10.89627722436882</v>
       </c>
       <c r="D10" t="n">
-        <v>66.5997806855782</v>
+        <v>10.82246436140646</v>
       </c>
       <c r="E10" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F10" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.46348649432197</v>
+        <v>2.18781655532732</v>
       </c>
       <c r="D11" t="n">
-        <v>13.7288416214718</v>
+        <v>2.230936763489168</v>
       </c>
       <c r="E11" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F11" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>55.12680497021559</v>
+        <v>8.958105807660033</v>
       </c>
       <c r="D12" t="n">
-        <v>56.24975083654837</v>
+        <v>9.14058451093911</v>
       </c>
       <c r="E12" t="n">
-        <v>23.97611909123956</v>
+        <v>3.896119352326429</v>
       </c>
       <c r="F12" t="n">
-        <v>23.41833205682964</v>
+        <v>3.805478959234817</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
